--- a/results/protocols/final-candidate_MANDATORY_STRESS.xlsx
+++ b/results/protocols/final-candidate_MANDATORY_STRESS.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-20T06:21:46+00:00</t>
+          <t>2026-09-20T06:28:54+00:00</t>
         </is>
       </c>
     </row>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-20T06:21:46+00:00</t>
+          <t>2026-09-20T06:28:54+00:00</t>
         </is>
       </c>
     </row>
